--- a/cuadros/MAYO/CIRCULO MILITAR.xlsx
+++ b/cuadros/MAYO/CIRCULO MILITAR.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\MAYO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5711027E-3E45-4925-BE27-7173B00E0852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -64,33 +58,51 @@
     <t>FOTO_INCIDENCIA</t>
   </si>
   <si>
+    <t>CIRCULO MILITAR</t>
+  </si>
+  <si>
+    <t>CIRCULO</t>
+  </si>
+  <si>
+    <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+  </si>
+  <si>
+    <t>LA CARIDAD C.A.</t>
+  </si>
+  <si>
+    <t>YEFFERSON MAY MORGADO CHACON</t>
+  </si>
+  <si>
+    <t>CAVA LUXOR</t>
+  </si>
+  <si>
     <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
   </si>
   <si>
-    <t>AGROPECUARIA LATIN FRUITS C.A.</t>
-  </si>
-  <si>
-    <t>LA CARIDAD C.A.</t>
-  </si>
-  <si>
-    <t>YEFFERSON MAY MORGADO CHACON</t>
-  </si>
-  <si>
-    <t>CAVA LUXOR</t>
+    <t>Alimentos Polar Comercial C.A.</t>
   </si>
   <si>
     <t>*106925</t>
   </si>
   <si>
+    <t>000613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7242093202 </t>
+  </si>
+  <si>
+    <t>7242093204</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
     <t>2026-05-04</t>
   </si>
   <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -103,25 +115,31 @@
     <t>SPCP HILDEMAR BUENO</t>
   </si>
   <si>
+    <t>EL PROVEEDOR</t>
+  </si>
+  <si>
+    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+  </si>
+  <si>
+    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+  </si>
+  <si>
     <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
   </si>
   <si>
-    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+    <t>OTRAS.</t>
+  </si>
+  <si>
+    <t>TIPO A</t>
+  </si>
+  <si>
+    <t>TIPO C</t>
   </si>
   <si>
     <t>TIPO D</t>
   </si>
   <si>
-    <t>TIPO A</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>FALTANTE DE 1KG DE YUCA CANCELADO EN TIENDA POR UN TOTAL DE 1321.79BS O 2.7$ AL CAMBIO DEL DÍA DE HOY.</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>EL NÚMERO DE CONTROL INGRESADO EN EL SISTEMA ES INCORRECTO, EL CORRECTO ES: 0000010136</t>
@@ -136,44 +154,62 @@
     <t>SE CARGARON POR ERROR LOS SIGUIENTES SKU EN EL SISTEMA: LIM5612, LIM5613, LIM5678, LIM5611, LIM5614 Y LIMPI41.</t>
   </si>
   <si>
-    <t>113659.jpeg</t>
+    <t>Durante la recepción de Yuca del 4/05/2026, se recibieron 64.5kg brutos, restando las 2 taras de 2.8kg (5.6kg) para un total de 58.9Kg de peso neto, sin embargo, al contrastar esto con los 59.9kg colocados en factura se determina un faltante de 1kg de yuca. Dicho faltante fue cancelado en la sucursal pagando un total de 1321.79Bs o 2.7$ al cambio del día</t>
+  </si>
+  <si>
+    <t>Durante la recepción el responsable realizó el pago de tres (3) unidades de "Detergente Las Llaves Floral Limpieza Activa de 900Gr" averiadas para no generar un faltante en la factura, el pago total fueron 3888.17Bs o 7.93$ al cambio del día.</t>
+  </si>
+  <si>
+    <t>Durante la recepción el responsable realizó el pago de una (1) unidad de "Alimento para perro Dogourmet Carne a la Parrilla de 1kg" averiada para no generar un faltante en la factura, el pago total fueron 2540.96Bs o 5.19$ al cambio del día.</t>
   </si>
   <si>
     <t>SIN_FOTO</t>
   </si>
   <si>
+    <t>00113659.jpeg</t>
+  </si>
+  <si>
+    <t>00098633.jpg</t>
+  </si>
+  <si>
+    <t>00100940.jpg</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
     <t>COBRO</t>
   </si>
   <si>
-    <t>NINGUNA</t>
+    <t>ID_20260506093212</t>
+  </si>
+  <si>
+    <t>ID_20260506094506</t>
+  </si>
+  <si>
+    <t>ID_20260506162223</t>
+  </si>
+  <si>
+    <t>ID_20260506162827</t>
   </si>
   <si>
     <t>HIST_20260504162447</t>
   </si>
   <si>
-    <t>ID_20260506093212</t>
-  </si>
-  <si>
-    <t>ID_20260506094506</t>
-  </si>
-  <si>
-    <t>ID_20260506162223</t>
-  </si>
-  <si>
-    <t>ID_20260506162827</t>
-  </si>
-  <si>
-    <t>undefined</t>
-  </si>
-  <si>
-    <t>CIRCULO MILITAR</t>
+    <t>ID_20260506165102</t>
+  </si>
+  <si>
+    <t>ID_20260506165341</t>
+  </si>
+  <si>
+    <t>INC_164450.jpeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,19 +246,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -264,7 +292,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -296,27 +324,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -348,24 +358,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -541,14 +533,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="30.61328125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -592,212 +581,291 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>6519</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="C2">
-        <v>613</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2">
-        <v>2.7</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>469620</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <v>6519</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>469620</v>
+        <v>126076</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>39</v>
       </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>126076</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6">
+        <v>2.7</v>
+      </c>
+      <c r="K6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>7.93</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
         <v>41</v>
       </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="I8" t="s">
         <v>48</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>46</v>
+      <c r="J8">
+        <v>5.19</v>
+      </c>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/CIRCULO MILITAR.xlsx
+++ b/cuadros/MAYO/CIRCULO MILITAR.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -56,7 +57,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,11 +975,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Durante la recepción el responsable realizó el pago de una (1) unidad de "Pasta Capri Premium Rigatoni de 1kg" averiada para no generar un faltante en la factura, el pago total fueron 912.75Bs o 1.85$ al cambio del día.</t>
@@ -1003,7 +999,527 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HIDROPONIAS VENEZOLANAS, C.A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20111017</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SPCP MACKENZY A. RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SE CARGO POR ERROR EL AJO EN MALLA POR KG EL CUAL NO PERTENECE A ESTA RECEPCIÓN</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260511142210</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>000790</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SPCP JESUS A. PACHECO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AL MOMENTO DE FIRMAR LA FACTURA RECEPCIONADA EL SPCP NO COLOCO SU CÉDULA</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260511142348</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INVERSIONES RUBYMAR R.M C.A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>008768</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SPCP JESUS A. PACHECO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AL MOMENTO DE FIRMAR LA FACTURA RECEPCIONADA EL SPCP NO COLOCO SU CÉDULA</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260511142449</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>020559</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SPCP MACKENZY A. RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SE AGREGO AL SISTEMA POR ERROR "POLLO ENTERO FRESCO" SIENDO QUE SE ESTABA RECIBIENDO "POLLO ENTERO CONGELADO"</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260511142919</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>020559</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MACKENZY A. RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FALTO AGREGAR LA TARA AL PESAJE DEL "POLLO ENTERO CONGELADO" SIENDO ESTA UNA (1) TARA DE 2.3KG</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260511143034</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LACTEOS CORRALITO, F.P.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>000710</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SPCP JESUS A. PACHECO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AL MOMENTO DE FIRMAR LA FACTURA EL SPCP NO COLOCO SU CÉDULA</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ID_20260511143251</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA H2O DE COCO, C.A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>001260</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SPCP JONATAN R. TOVAR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NÚMERO DE FACTURA CORRECTO: 001271 NÚMERO DE CONTROL CORRECTO: 00001271</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ID_20260511143432</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SPCP JONATAN R. TOVAR</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LA DOCUMENTACIÓN AGREGADA EN LA APLICACIÓN ES INCORRECTA</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ID_20260511144426</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/CIRCULO MILITAR.xlsx
+++ b/cuadros/MAYO/CIRCULO MILITAR.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -421,7 +420,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="28.4609375" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -752,7 +754,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CIRCULO</t>
+          <t>CIRCULO MILITAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/cuadros/MAYO/CIRCULO MILITAR.xlsx
+++ b/cuadros/MAYO/CIRCULO MILITAR.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -419,11 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="28.4609375" customWidth="1" min="1" max="1"/>
-  </cols>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -508,8 +505,10 @@
           <t>AGROPECUARIA LATIN FRUITS C.A.</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>6519</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6519</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -571,8 +570,10 @@
           <t>LA CARIDAD C.A.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>469620</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>469620</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -634,8 +635,10 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>126076</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>126076</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1521,7 +1524,72 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CIRCULO MILITAR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>006657</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DANIHEL J. PALACIOS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EL NÚMERO DE CONTROL COLOCADO EN LA APLICACIÓN ES INCORRECTO, EL CORRECTO ES: 0000010344</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ID_20260515153705</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>